--- a/Data/Qualitative analysis results/curated agent.xlsx
+++ b/Data/Qualitative analysis results/curated agent.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xingqian/Desktop/msr_replication_package/Data/Qualitative analysis results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xingqian/Desktop/PR_replication_package/Data/Qualitative analysis results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599C5E0F-F77C-E74E-A7B3-95BBA568962D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E42CA5-1D8C-5748-9257-0B6A33F7D44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6520" yWindow="2800" windowWidth="28040" windowHeight="17180" xr2:uid="{F6602C1A-4DBF-0845-837A-21C75D7DCBA7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="220">
   <si>
     <t>curated agent</t>
   </si>
@@ -511,12 +511,204 @@
   <si>
     <t>https://github.com/calcom/cal.com/pull/21460/commits/c6e7dfae3b86d0c2eb0b09955a73cfb7eb654c25</t>
   </si>
+  <si>
+    <t>https://github.com/GrantBirki/pr-status/pull/37</t>
+  </si>
+  <si>
+    <t>https://github.com/timfee/scheduler/pull/88</t>
+  </si>
+  <si>
+    <t>Parameterize method</t>
+  </si>
+  <si>
+    <t>https://github.com/mholzi/home_trivia/pull/11</t>
+  </si>
+  <si>
+    <t>Direct removal</t>
+  </si>
+  <si>
+    <t>https://github.com/Asoc-Hacker-Dreams/xopsmainpage-react/pull/28</t>
+  </si>
+  <si>
+    <t>direct removal</t>
+  </si>
+  <si>
+    <t>https://github.com/stastnypremysl/nautilus_trader/pull/12</t>
+  </si>
+  <si>
+    <t>https://github.com/luishdz044/MUPAI/pull/1</t>
+  </si>
+  <si>
+    <t>https://github.com/lesven/onboarder/pull/23</t>
+  </si>
+  <si>
+    <t>https://github.com/ZoneCog/elizaos-cpp/pull/98</t>
+  </si>
+  <si>
+    <t>https://github.com/b6428259/trip-planner-app/pull/3</t>
+  </si>
+  <si>
+    <t>https://github.com/vsvandelik/xxp-tooling-v2/pull/53</t>
+  </si>
+  <si>
+    <t>not pass</t>
+  </si>
+  <si>
+    <t>https://github.com/openUC2/ImSwitch/pull/100</t>
+  </si>
+  <si>
+    <t>https://github.com/mholzi/Soundbeats/pull/171</t>
+  </si>
+  <si>
+    <t>https://github.com/JFolberth/ai-in-a-box/pull/94</t>
+  </si>
+  <si>
+    <t>https://github.com/CyanAutomation/judokon/pull/337</t>
+  </si>
+  <si>
+    <t>move method</t>
+  </si>
+  <si>
+    <t>https://github.com/atxtechbro/dotfiles/pull/221</t>
+  </si>
+  <si>
+    <t>https://github.com/SlavaShorkin/-/pull/5</t>
+  </si>
+  <si>
+    <t>https://github.com/Yukaii/tailportal/pull/13</t>
+  </si>
+  <si>
+    <t>extract class</t>
+  </si>
+  <si>
+    <t>https://github.com/JFolberth/ai-in-a-box/pull/136</t>
+  </si>
+  <si>
+    <t>https://github.com/liuxiao2015/game-server-framework/pull/71</t>
+  </si>
+  <si>
+    <t>https://github.com/dayour/Power-Agent-MCP/pull/10</t>
+  </si>
+  <si>
+    <t>https://github.com/invokable/laravel-bluesky/pull/33</t>
+  </si>
+  <si>
+    <t>https://github.com/pydlv/xcode/pull/16</t>
+  </si>
+  <si>
+    <t>https://github.com/pydlv/xcode/pull/20</t>
+  </si>
+  <si>
+    <t>https://github.com/Azure/azure-dev/pull/5368</t>
+  </si>
+  <si>
+    <t>https://github.com/rosssaunders/ccrxt/pull/313</t>
+  </si>
+  <si>
+    <t>https://github.com/pydlv/xcode/pull/28</t>
+  </si>
+  <si>
+    <t>pull up method</t>
+  </si>
+  <si>
+    <t>https://github.com/pydlv/xcode/pull/36</t>
+  </si>
+  <si>
+    <t>https://github.com/efischer19/hoopstat-haus/pull/33</t>
+  </si>
+  <si>
+    <t>did not remove clone</t>
+  </si>
+  <si>
+    <t>https://github.com/jmbish04/cloudflare-agentic-ai-browser/pull/32</t>
+  </si>
+  <si>
+    <t>https://github.com/stangelika/LensDataBase/pull/15</t>
+  </si>
+  <si>
+    <t>https://github.com/GenghisDarb/AI-Minesweeper-Discovery-Framework/pull/33</t>
+  </si>
+  <si>
+    <t>no review</t>
+  </si>
+  <si>
+    <t>AI only</t>
+  </si>
+  <si>
+    <t>https://github.com/ahmedmuhi/whisper-transcribe/pull/48</t>
+  </si>
+  <si>
+    <t>https://github.com/ahmedmuhi/whisper-transcribe/pull/50</t>
+  </si>
+  <si>
+    <t>https://github.com/AshishMahendra/happy-sprout-journey-app-dev/pull/1</t>
+  </si>
+  <si>
+    <t>https://github.com/Wotusay/MCP-testing/pull/24</t>
+  </si>
+  <si>
+    <t>extract superclass</t>
+  </si>
+  <si>
+    <t>https://github.com/zaxiom13/MemoryWhole/pull/34</t>
+  </si>
+  <si>
+    <t>https://github.com/GaryOcean428/gary-zero/pull/223</t>
+  </si>
+  <si>
+    <t>https://github.com/LarsDenBakker/larsworld/pull/26</t>
+  </si>
+  <si>
+    <t>https://github.com/anon987654321/pub/pull/140</t>
+  </si>
+  <si>
+    <t>https://github.com/ublue-os/bluefin-docs/pull/270</t>
+  </si>
+  <si>
+    <t>https://github.com/g-kari/multiple-qr-reader/pull/6</t>
+  </si>
+  <si>
+    <t>https://github.com/BarbourSmith/Abundance/pull/454</t>
+  </si>
+  <si>
+    <t>https://github.com/timfee/scheduler/pull/170</t>
+  </si>
+  <si>
+    <t>https://github.com/NotRatz/kexplorer/pull/8</t>
+  </si>
+  <si>
+    <t>https://github.com/zoran123456/PathFollowingExample/pull/8</t>
+  </si>
+  <si>
+    <t>https://github.com/3amon/LoRaPeerLink/pull/39</t>
+  </si>
+  <si>
+    <t>https://github.com/Onivoid/rollaway/pull/3</t>
+  </si>
+  <si>
+    <t>https://github.com/nagiyu/niconico-mylist-assistant/pull/98</t>
+  </si>
+  <si>
+    <t>https://github.com/petrroll/illdata/pull/22</t>
+  </si>
+  <si>
+    <t>https://github.com/mcclowes/ai-art/pull/37</t>
+  </si>
+  <si>
+    <t>https://github.com/sssdesu/CloudflareWorker/pull/4</t>
+  </si>
+  <si>
+    <t>https://github.com/tosi29/app/pull/102</t>
+  </si>
+  <si>
+    <t>https://github.com/3amon/LoRaPeerLink/pull/8</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -547,6 +739,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -569,7 +768,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -581,11 +780,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -921,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21800A4F-E1F1-2B4B-BBEA-21C1C5136870}">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="12" max="12" width="36" customWidth="1"/>
@@ -935,20 +1135,20 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
       <c r="E1" s="2"/>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5" t="s">
+      <c r="G1" s="7"/>
+      <c r="H1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="5"/>
+      <c r="I1" s="7"/>
       <c r="J1" s="3" t="s">
         <v>4</v>
       </c>
@@ -1005,8 +1205,8 @@
       <c r="K2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -1042,10 +1242,10 @@
       <c r="K3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="6" t="s">
         <v>69</v>
       </c>
       <c r="N3" s="3" t="s">
@@ -1088,10 +1288,10 @@
       <c r="K4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M4" s="6"/>
+      <c r="M4" s="5"/>
       <c r="N4" s="3" t="s">
         <v>42</v>
       </c>
@@ -1132,10 +1332,10 @@
       <c r="K5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="M5" s="6" t="s">
         <v>72</v>
       </c>
       <c r="N5" s="3" t="s">
@@ -1180,10 +1380,10 @@
       <c r="K6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="6" t="s">
         <v>74</v>
       </c>
       <c r="N6" s="3" t="s">
@@ -1226,10 +1426,10 @@
       <c r="K7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="M7" s="7" t="s">
+      <c r="M7" s="6" t="s">
         <v>76</v>
       </c>
       <c r="N7" s="3" t="s">
@@ -1274,10 +1474,10 @@
       <c r="K8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="6" t="s">
         <v>78</v>
       </c>
       <c r="N8" s="3" t="s">
@@ -1319,10 +1519,10 @@
       <c r="K9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="M9" s="6" t="s">
         <v>80</v>
       </c>
       <c r="N9" s="3" t="s">
@@ -1366,10 +1566,10 @@
       <c r="K10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L10" s="7" t="s">
+      <c r="L10" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="M10" s="6" t="s">
         <v>82</v>
       </c>
       <c r="N10" s="3" t="s">
@@ -1411,10 +1611,10 @@
       <c r="K11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="6" t="s">
         <v>84</v>
       </c>
       <c r="N11" s="3" t="s">
@@ -1456,10 +1656,10 @@
       <c r="K12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="6" t="s">
         <v>86</v>
       </c>
       <c r="N12" s="3" t="s">
@@ -1501,10 +1701,10 @@
       <c r="K13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="M13" s="7" t="s">
+      <c r="M13" s="6" t="s">
         <v>88</v>
       </c>
       <c r="N13" s="3" t="s">
@@ -1546,10 +1746,10 @@
       <c r="K14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="M14" s="7" t="s">
+      <c r="M14" s="6" t="s">
         <v>90</v>
       </c>
       <c r="N14" s="3" t="s">
@@ -1591,10 +1791,10 @@
       <c r="K15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="7" t="s">
+      <c r="L15" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="M15" s="6" t="s">
         <v>92</v>
       </c>
       <c r="N15" s="3" t="s">
@@ -1636,10 +1836,10 @@
       <c r="K16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="L16" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="M16" s="6" t="s">
         <v>94</v>
       </c>
       <c r="N16" s="3" t="s">
@@ -1681,10 +1881,10 @@
       <c r="K17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="7" t="s">
+      <c r="L17" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="M17" s="7" t="s">
+      <c r="M17" s="6" t="s">
         <v>96</v>
       </c>
       <c r="N17" s="3" t="s">
@@ -1726,10 +1926,10 @@
       <c r="K18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L18" s="7" t="s">
+      <c r="L18" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="M18" s="7" t="s">
+      <c r="M18" s="6" t="s">
         <v>98</v>
       </c>
       <c r="N18" s="3" t="s">
@@ -1773,10 +1973,10 @@
       <c r="K19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L19" s="7" t="s">
+      <c r="L19" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="M19" s="7" t="s">
+      <c r="M19" s="6" t="s">
         <v>100</v>
       </c>
       <c r="N19" s="3" t="s">
@@ -1818,10 +2018,10 @@
       <c r="K20" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L20" s="7" t="s">
+      <c r="L20" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="M20" s="7" t="s">
+      <c r="M20" s="6" t="s">
         <v>102</v>
       </c>
       <c r="N20" s="3" t="s">
@@ -1868,10 +2068,10 @@
       <c r="K21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L21" s="7" t="s">
+      <c r="L21" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="M21" s="7" t="s">
+      <c r="M21" s="6" t="s">
         <v>104</v>
       </c>
       <c r="N21" s="3" t="s">
@@ -1914,10 +2114,10 @@
       <c r="K22" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="7" t="s">
+      <c r="L22" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="M22" s="7" t="s">
+      <c r="M22" s="6" t="s">
         <v>106</v>
       </c>
       <c r="N22" s="3" t="s">
@@ -1960,10 +2160,10 @@
       <c r="K23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L23" s="7" t="s">
+      <c r="L23" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="M23" s="7" t="s">
+      <c r="M23" s="6" t="s">
         <v>108</v>
       </c>
       <c r="N23" s="3" t="s">
@@ -2008,10 +2208,10 @@
       <c r="K24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L24" s="7" t="s">
+      <c r="L24" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="M24" s="7" t="s">
+      <c r="M24" s="6" t="s">
         <v>110</v>
       </c>
       <c r="N24" s="3" t="s">
@@ -2058,10 +2258,10 @@
       <c r="K25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L25" s="7" t="s">
+      <c r="L25" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="M25" s="7" t="s">
+      <c r="M25" s="6" t="s">
         <v>112</v>
       </c>
       <c r="N25" s="3" t="s">
@@ -2104,10 +2304,10 @@
       <c r="K26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L26" s="7" t="s">
+      <c r="L26" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="M26" s="7" t="s">
+      <c r="M26" s="6" t="s">
         <v>114</v>
       </c>
       <c r="N26" s="3" t="s">
@@ -2154,10 +2354,10 @@
       <c r="K27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L27" s="7" t="s">
+      <c r="L27" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="M27" s="7" t="s">
+      <c r="M27" s="6" t="s">
         <v>116</v>
       </c>
       <c r="N27" s="3" t="s">
@@ -2200,10 +2400,10 @@
       <c r="K28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L28" s="7" t="s">
+      <c r="L28" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="M28" s="7" t="s">
+      <c r="M28" s="6" t="s">
         <v>118</v>
       </c>
       <c r="N28" s="3" t="s">
@@ -2248,10 +2448,10 @@
       <c r="K29" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L29" s="7" t="s">
+      <c r="L29" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="M29" s="7" t="s">
+      <c r="M29" s="6" t="s">
         <v>120</v>
       </c>
       <c r="N29" s="3" t="s">
@@ -2298,10 +2498,10 @@
       <c r="K30" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L30" s="7" t="s">
+      <c r="L30" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="M30" s="7" t="s">
+      <c r="M30" s="6" t="s">
         <v>122</v>
       </c>
       <c r="N30" s="3" t="s">
@@ -2348,10 +2548,10 @@
       <c r="K31" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L31" s="7" t="s">
+      <c r="L31" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="M31" s="7" t="s">
+      <c r="M31" s="6" t="s">
         <v>124</v>
       </c>
       <c r="N31" s="3" t="s">
@@ -2396,10 +2596,10 @@
       <c r="K32" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L32" s="7" t="s">
+      <c r="L32" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="M32" s="7" t="s">
+      <c r="M32" s="6" t="s">
         <v>126</v>
       </c>
       <c r="N32" s="3" t="s">
@@ -2443,10 +2643,10 @@
       <c r="K33" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L33" s="7" t="s">
+      <c r="L33" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="M33" s="7" t="s">
+      <c r="M33" s="6" t="s">
         <v>128</v>
       </c>
       <c r="N33" s="3" t="s">
@@ -2490,10 +2690,10 @@
       <c r="K34" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L34" s="7" t="s">
+      <c r="L34" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="M34" s="6"/>
+      <c r="M34" s="5"/>
       <c r="N34" s="3" t="s">
         <v>42</v>
       </c>
@@ -2535,10 +2735,10 @@
       <c r="K35" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L35" s="7" t="s">
+      <c r="L35" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="M35" s="7" t="s">
+      <c r="M35" s="6" t="s">
         <v>131</v>
       </c>
       <c r="N35" s="3" t="s">
@@ -2579,10 +2779,10 @@
       <c r="K36" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L36" s="7" t="s">
+      <c r="L36" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="M36" s="7" t="s">
+      <c r="M36" s="6" t="s">
         <v>133</v>
       </c>
       <c r="N36" s="3" t="s">
@@ -2626,10 +2826,10 @@
       <c r="K37" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L37" s="7" t="s">
+      <c r="L37" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="M37" s="7" t="s">
+      <c r="M37" s="6" t="s">
         <v>135</v>
       </c>
       <c r="N37" s="3" t="s">
@@ -2673,10 +2873,10 @@
       <c r="K38" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L38" s="7" t="s">
+      <c r="L38" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="M38" s="7" t="s">
+      <c r="M38" s="6" t="s">
         <v>137</v>
       </c>
       <c r="N38" s="3" t="s">
@@ -2718,10 +2918,10 @@
       <c r="K39" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L39" s="7" t="s">
+      <c r="L39" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="M39" s="7" t="s">
+      <c r="M39" s="6" t="s">
         <v>139</v>
       </c>
       <c r="N39" s="3" t="s">
@@ -2766,10 +2966,10 @@
       <c r="K40" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L40" s="7" t="s">
+      <c r="L40" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="M40" s="7" t="s">
+      <c r="M40" s="6" t="s">
         <v>141</v>
       </c>
       <c r="N40" s="3" t="s">
@@ -2814,10 +3014,10 @@
       <c r="K41" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L41" s="7" t="s">
+      <c r="L41" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="M41" s="7" t="s">
+      <c r="M41" s="6" t="s">
         <v>143</v>
       </c>
       <c r="N41" s="3" t="s">
@@ -2860,10 +3060,10 @@
       <c r="K42" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L42" s="7" t="s">
+      <c r="L42" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="M42" s="7" t="s">
+      <c r="M42" s="6" t="s">
         <v>145</v>
       </c>
       <c r="N42" s="3" t="s">
@@ -2910,10 +3110,10 @@
       <c r="K43" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="L43" s="7" t="s">
+      <c r="L43" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="M43" s="7" t="s">
+      <c r="M43" s="6" t="s">
         <v>147</v>
       </c>
       <c r="N43" s="3" t="s">
@@ -2958,10 +3158,10 @@
       <c r="K44" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L44" s="7" t="s">
+      <c r="L44" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="M44" s="7" t="s">
+      <c r="M44" s="6" t="s">
         <v>149</v>
       </c>
       <c r="N44" s="3" t="s">
@@ -3006,10 +3206,10 @@
       <c r="K45" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L45" s="7" t="s">
+      <c r="L45" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="M45" s="7" t="s">
+      <c r="M45" s="6" t="s">
         <v>151</v>
       </c>
       <c r="N45" s="3" t="s">
@@ -3054,10 +3254,10 @@
       <c r="K46" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L46" s="7" t="s">
+      <c r="L46" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="M46" s="7" t="s">
+      <c r="M46" s="6" t="s">
         <v>153</v>
       </c>
       <c r="N46" s="3" t="s">
@@ -3102,10 +3302,10 @@
       <c r="K47" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="L47" s="7" t="s">
+      <c r="L47" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="M47" s="7" t="s">
+      <c r="M47" s="6" t="s">
         <v>155</v>
       </c>
       <c r="N47" s="3" t="s">
@@ -3117,6 +3317,2426 @@
       <c r="P47" s="3" t="s">
         <v>64</v>
       </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A48" s="8">
+        <v>3221054244</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A49" s="8">
+        <v>3221159679</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="M49" s="3"/>
+      <c r="N49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O49" s="3"/>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A50" s="8">
+        <v>3129054890</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A51" s="8">
+        <v>3124664441</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="O51" s="3"/>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A52" s="8">
+        <v>3151224777</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A53" s="8">
+        <v>3151327208</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="M53" s="3"/>
+      <c r="N53" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="O53" s="3"/>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A54" s="8">
+        <v>3261969248</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A55" s="8">
+        <v>3261984739</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A56" s="8">
+        <v>3262012261</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A57" s="8">
+        <v>3190511360</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A58" s="8">
+        <v>3174556791</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A59" s="8">
+        <v>3125804926</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="M59" s="3"/>
+      <c r="N59" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O59" s="3"/>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A60" s="8">
+        <v>3125961260</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" s="8">
+        <v>3179810646</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" s="8">
+        <v>3179900543</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A63" s="8">
+        <v>3078107049</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="M63" s="3"/>
+      <c r="N63" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="O63" s="3"/>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A64" s="8">
+        <v>3231540507</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O64" s="3"/>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A65" s="8">
+        <v>3121381089</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="M65" s="3"/>
+      <c r="N65" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="O65" s="3"/>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A66" s="8">
+        <v>3195874121</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O66" s="3"/>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A67" s="8">
+        <v>3106737004</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A68" s="8">
+        <v>3151884647</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A69" s="8">
+        <v>3152059147</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L69" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="O69" s="3"/>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A70" s="8">
+        <v>3152064733</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A71" s="8">
+        <v>3152107061</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L71" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O71" s="3"/>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A72" s="8">
+        <v>3152145544</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A73" s="8">
+        <v>3152358735</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="M73" s="3"/>
+      <c r="N73" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="O73" s="3"/>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A74" s="8">
+        <v>3152424553</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A75" s="8">
+        <v>3152559820</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="M75" s="3"/>
+      <c r="N75" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="O75" s="3"/>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A76" s="8">
+        <v>3241328319</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A77" s="8">
+        <v>3241399602</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="O77" s="3"/>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A78" s="8">
+        <v>3241442005</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A79" s="8">
+        <v>3247591708</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="O79" s="3"/>
+      <c r="P79" s="3"/>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A80" s="8">
+        <v>3234998236</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A81" s="8">
+        <v>3235118814</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="M81" s="3"/>
+      <c r="N81" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O81" s="3"/>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A82" s="8">
+        <v>3262605528</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A83" s="8">
+        <v>3273505818</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="O83" s="3"/>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A84" s="8">
+        <v>3084128612</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="O84" s="3"/>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A85" s="8">
+        <v>3253002070</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O85" s="3"/>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A86" s="8">
+        <v>3276833220</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O86" s="3"/>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A87" s="8">
+        <v>3276908120</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="M87" s="3"/>
+      <c r="N87" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="O87" s="3"/>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A88" s="8">
+        <v>3276958828</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O88" s="3"/>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A89" s="8">
+        <v>3140171093</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="M89" s="3"/>
+      <c r="N89" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O89" s="3"/>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A90" s="8">
+        <v>3157434617</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J90" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K90" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A91" s="8">
+        <v>3224751752</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M91" s="3"/>
+      <c r="N91" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O91" s="3"/>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A92" s="8">
+        <v>3203914553</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="O92" s="3"/>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A93" s="8">
+        <v>3079837515</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="M93" s="3"/>
+      <c r="N93" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="O93" s="3"/>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A94" s="8">
+        <v>3177322961</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="M94" s="3"/>
+      <c r="N94" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="O94" s="3"/>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A95" s="8">
+        <v>3212294729</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J95" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="M95" s="3"/>
+      <c r="N95" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A96" s="8">
+        <v>3230608495</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O96" s="3"/>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A97" s="8">
+        <v>3194137038</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J97" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L97" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="M97" s="3"/>
+      <c r="N97" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O97" s="3"/>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A98" s="8">
+        <v>3105219276</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J98" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O98" s="3"/>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A99" s="8">
+        <v>3239697361</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J99" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K99" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L99" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="M99" s="3"/>
+      <c r="N99" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O99" s="3"/>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A100" s="8">
+        <v>3092181470</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L100" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="M100" s="3"/>
+      <c r="N100" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="O100" s="3"/>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A101" s="8">
+        <v>3102019298</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L101" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="O101" s="3"/>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A102" s="8">
+        <v>3169319172</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L102" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="M102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
